--- a/tables/datas/common/#DropGroup-掉落组表.xlsx
+++ b/tables/datas/common/#DropGroup-掉落组表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,36 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>野狼王掉落</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1002,1,3,80,true|2001,1,1,30,false|1006,1,1,5,false</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>白银野狼掉落</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1002,1,2,60,true|2001,1,1,20,false|1006,1,1,15,false</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
